--- a/artfynd/A 26084-2025 artfynd.xlsx
+++ b/artfynd/A 26084-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1457,6 +1457,3262 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128790214</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91466</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stor-Orrmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>622474</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6973956</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128790233</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57849</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stor-Orrmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>622221</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6974121</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Lockläte/övriga läten</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128790237</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91762</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>658</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stor-Orrmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>622211</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6974148</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128790218</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91466</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stor-Orrmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>622266</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6974203</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128790241</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80194</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stor-Orrmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>622266</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6974089</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128790230</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57689</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Stor-Orrmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>622493</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6973939</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128790232</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57849</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stor-Orrmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>622266</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6974205</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128790244</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91484</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Stor-Orrmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>622463</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6973956</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128790217</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91466</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Stor-Orrmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>622309</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6974038</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128790234</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80223</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Stor-Orrmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>622437</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6973961</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128790238</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91762</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>658</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Stor-Orrmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>622403</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6974067</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128790235</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80223</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Stor-Orrmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>622326</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6974111</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128790220</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91466</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Stor-Orrmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>622295</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6974119</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128790224</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57689</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Stor-Orrmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>622566</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6973722</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128790228</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57689</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Stor-Orrmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>622637</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6973628</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128790245</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79089</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Stor-Orrmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>622540</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6973635</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128790225</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57689</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Stor-Orrmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>622560</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6973750</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>1 ex födosökande</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128790239</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80194</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Stor-Orrmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>622436</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6973957</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128790246</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79089</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Stor-Orrmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>622548</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6973896</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128790216</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91466</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Stor-Orrmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>622450</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6974017</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128790240</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80194</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Stor-Orrmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>622574</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6973694</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128790226</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57689</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Stor-Orrmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>622549</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6973550</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>1 ex födosökande</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128790222</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91466</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Stor-Orrmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>622227</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6974127</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128790229</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57689</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Stor-Orrmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>622639</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6973634</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128790223</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57689</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Stor-Orrmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>622582</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6973719</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128790248</v>
+      </c>
+      <c r="B34" t="n">
+        <v>80229</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Stor-Orrmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>622568</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6973700</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128790219</v>
+      </c>
+      <c r="B35" t="n">
+        <v>91466</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Stor-Orrmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>622240</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6974241</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128790231</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57849</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Stor-Orrmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>622564</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6973544</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Lockläte/övriga läten</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128790213</v>
+      </c>
+      <c r="B37" t="n">
+        <v>91431</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Stor-Orrmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>622224</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6974135</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128790236</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57686</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Stor-Orrmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>622264</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6974088</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128790247</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79089</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Stor-Orrmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>622267</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6974268</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128790221</v>
+      </c>
+      <c r="B40" t="n">
+        <v>91466</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Stor-Orrmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>622221</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6974149</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128790227</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57689</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Stor-Orrmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>622646</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6973525</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Härnösand</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Viksjö</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26084-2025 artfynd.xlsx
+++ b/artfynd/A 26084-2025 artfynd.xlsx
@@ -1462,7 +1462,7 @@
         <v>128790214</v>
       </c>
       <c r="B9" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128790233</v>
+        <v>128790237</v>
       </c>
       <c r="B10" t="n">
-        <v>57849</v>
+        <v>91763</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1567,21 +1567,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>622221</v>
+        <v>622211</v>
       </c>
       <c r="R10" t="n">
-        <v>6974121</v>
+        <v>6974148</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,11 +1627,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1658,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128790237</v>
+        <v>128790233</v>
       </c>
       <c r="B11" t="n">
-        <v>91762</v>
+        <v>57849</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,21 +1664,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1693,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>622211</v>
+        <v>622221</v>
       </c>
       <c r="R11" t="n">
-        <v>6974148</v>
+        <v>6974121</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,6 +1724,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1758,7 +1758,7 @@
         <v>128790218</v>
       </c>
       <c r="B12" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2051,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128790232</v>
+        <v>128790244</v>
       </c>
       <c r="B15" t="n">
-        <v>57849</v>
+        <v>91485</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2062,21 +2062,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>622266</v>
+        <v>622463</v>
       </c>
       <c r="R15" t="n">
-        <v>6974205</v>
+        <v>6973956</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,10 +2148,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128790244</v>
+        <v>128790232</v>
       </c>
       <c r="B16" t="n">
-        <v>91484</v>
+        <v>57849</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2159,21 +2159,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>622463</v>
+        <v>622266</v>
       </c>
       <c r="R16" t="n">
-        <v>6973956</v>
+        <v>6974205</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2245,32 +2245,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128790217</v>
+        <v>128790234</v>
       </c>
       <c r="B17" t="n">
-        <v>91466</v>
+        <v>80223</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>622309</v>
+        <v>622437</v>
       </c>
       <c r="R17" t="n">
-        <v>6974038</v>
+        <v>6973961</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2342,32 +2342,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128790234</v>
+        <v>128790217</v>
       </c>
       <c r="B18" t="n">
-        <v>80223</v>
+        <v>91467</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>622437</v>
+        <v>622309</v>
       </c>
       <c r="R18" t="n">
-        <v>6973961</v>
+        <v>6974038</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2442,7 +2442,7 @@
         <v>128790238</v>
       </c>
       <c r="B19" t="n">
-        <v>91762</v>
+        <v>91763</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>128790220</v>
       </c>
       <c r="B21" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>128790216</v>
       </c>
       <c r="B28" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>128790222</v>
       </c>
       <c r="B31" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3720,32 +3720,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128790229</v>
+        <v>128790248</v>
       </c>
       <c r="B32" t="n">
-        <v>57689</v>
+        <v>80229</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3755,10 +3755,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>622639</v>
+        <v>622568</v>
       </c>
       <c r="R32" t="n">
-        <v>6973634</v>
+        <v>6973700</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3791,11 +3791,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3924,32 +3919,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128790248</v>
+        <v>128790229</v>
       </c>
       <c r="B34" t="n">
-        <v>80229</v>
+        <v>57689</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3959,10 +3954,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>622568</v>
+        <v>622639</v>
       </c>
       <c r="R34" t="n">
-        <v>6973700</v>
+        <v>6973634</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3995,6 +3990,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4024,7 +4024,7 @@
         <v>128790219</v>
       </c>
       <c r="B35" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>128790213</v>
       </c>
       <c r="B37" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>128790221</v>
       </c>
       <c r="B40" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 26084-2025 artfynd.xlsx
+++ b/artfynd/A 26084-2025 artfynd.xlsx
@@ -1462,7 +1462,7 @@
         <v>128790214</v>
       </c>
       <c r="B9" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>128790237</v>
       </c>
       <c r="B10" t="n">
-        <v>91763</v>
+        <v>91790</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1653,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128790233</v>
+        <v>128790218</v>
       </c>
       <c r="B11" t="n">
-        <v>57849</v>
+        <v>91494</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,21 +1664,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>622221</v>
+        <v>622266</v>
       </c>
       <c r="R11" t="n">
-        <v>6974121</v>
+        <v>6974203</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,11 +1724,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128790218</v>
+        <v>128790233</v>
       </c>
       <c r="B12" t="n">
-        <v>91467</v>
+        <v>57876</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,21 +1761,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>622266</v>
+        <v>622221</v>
       </c>
       <c r="R12" t="n">
-        <v>6974203</v>
+        <v>6974121</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1826,6 +1821,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1855,7 +1855,7 @@
         <v>128790241</v>
       </c>
       <c r="B13" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>128790230</v>
       </c>
       <c r="B14" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>128790244</v>
       </c>
       <c r="B15" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>128790232</v>
       </c>
       <c r="B16" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>128790234</v>
       </c>
       <c r="B17" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>128790217</v>
       </c>
       <c r="B18" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>128790238</v>
       </c>
       <c r="B19" t="n">
-        <v>91763</v>
+        <v>91790</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>128790235</v>
       </c>
       <c r="B20" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>128790220</v>
       </c>
       <c r="B21" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>128790224</v>
       </c>
       <c r="B22" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2832,10 +2832,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128790228</v>
+        <v>128790245</v>
       </c>
       <c r="B23" t="n">
-        <v>57689</v>
+        <v>79116</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2843,21 +2843,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2867,10 +2867,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>622637</v>
+        <v>622540</v>
       </c>
       <c r="R23" t="n">
-        <v>6973628</v>
+        <v>6973635</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2903,11 +2903,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2934,10 +2929,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128790245</v>
+        <v>128790228</v>
       </c>
       <c r="B24" t="n">
-        <v>79089</v>
+        <v>57716</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2945,21 +2940,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2969,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>622540</v>
+        <v>622637</v>
       </c>
       <c r="R24" t="n">
-        <v>6973635</v>
+        <v>6973628</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3005,6 +3000,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3034,7 +3034,7 @@
         <v>128790225</v>
       </c>
       <c r="B25" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128790239</v>
+        <v>128790246</v>
       </c>
       <c r="B26" t="n">
-        <v>80194</v>
+        <v>79116</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3144,21 +3144,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>622436</v>
+        <v>622548</v>
       </c>
       <c r="R26" t="n">
-        <v>6973957</v>
+        <v>6973896</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3230,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128790246</v>
+        <v>128790239</v>
       </c>
       <c r="B27" t="n">
-        <v>79089</v>
+        <v>80221</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3241,21 +3241,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>622548</v>
+        <v>622436</v>
       </c>
       <c r="R27" t="n">
-        <v>6973896</v>
+        <v>6973957</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3330,7 +3330,7 @@
         <v>128790216</v>
       </c>
       <c r="B28" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>128790240</v>
       </c>
       <c r="B29" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>128790226</v>
       </c>
       <c r="B30" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>128790222</v>
       </c>
       <c r="B31" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3720,32 +3720,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128790248</v>
+        <v>128790223</v>
       </c>
       <c r="B32" t="n">
-        <v>80229</v>
+        <v>57716</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3755,10 +3755,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>622568</v>
+        <v>622582</v>
       </c>
       <c r="R32" t="n">
-        <v>6973700</v>
+        <v>6973719</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3791,6 +3791,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3817,10 +3822,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128790223</v>
+        <v>128790229</v>
       </c>
       <c r="B33" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3852,10 +3857,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>622582</v>
+        <v>622639</v>
       </c>
       <c r="R33" t="n">
-        <v>6973719</v>
+        <v>6973634</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3919,32 +3924,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128790229</v>
+        <v>128790248</v>
       </c>
       <c r="B34" t="n">
-        <v>57689</v>
+        <v>80256</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3954,10 +3959,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>622639</v>
+        <v>622568</v>
       </c>
       <c r="R34" t="n">
-        <v>6973634</v>
+        <v>6973700</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3990,11 +3995,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4024,7 +4024,7 @@
         <v>128790219</v>
       </c>
       <c r="B35" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         <v>128790231</v>
       </c>
       <c r="B36" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>128790213</v>
       </c>
       <c r="B37" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>128790236</v>
       </c>
       <c r="B38" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>128790247</v>
       </c>
       <c r="B39" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4516,10 +4516,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128790221</v>
+        <v>128790227</v>
       </c>
       <c r="B40" t="n">
-        <v>91467</v>
+        <v>57716</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4527,21 +4527,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4551,10 +4551,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>622221</v>
+        <v>622646</v>
       </c>
       <c r="R40" t="n">
-        <v>6974149</v>
+        <v>6973525</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4587,6 +4587,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4613,10 +4618,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128790227</v>
+        <v>128790221</v>
       </c>
       <c r="B41" t="n">
-        <v>57689</v>
+        <v>91494</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4624,21 +4629,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4648,10 +4653,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>622646</v>
+        <v>622221</v>
       </c>
       <c r="R41" t="n">
-        <v>6973525</v>
+        <v>6974149</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4684,11 +4689,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 26084-2025 artfynd.xlsx
+++ b/artfynd/A 26084-2025 artfynd.xlsx
@@ -3720,32 +3720,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128790223</v>
+        <v>128790248</v>
       </c>
       <c r="B32" t="n">
-        <v>57716</v>
+        <v>80256</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3755,10 +3755,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>622582</v>
+        <v>622568</v>
       </c>
       <c r="R32" t="n">
-        <v>6973719</v>
+        <v>6973700</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3791,11 +3791,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3822,7 +3817,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128790229</v>
+        <v>128790223</v>
       </c>
       <c r="B33" t="n">
         <v>57716</v>
@@ -3857,10 +3852,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>622639</v>
+        <v>622582</v>
       </c>
       <c r="R33" t="n">
-        <v>6973634</v>
+        <v>6973719</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3924,32 +3919,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128790248</v>
+        <v>128790229</v>
       </c>
       <c r="B34" t="n">
-        <v>80256</v>
+        <v>57716</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3959,10 +3954,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>622568</v>
+        <v>622639</v>
       </c>
       <c r="R34" t="n">
-        <v>6973700</v>
+        <v>6973634</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3995,6 +3990,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4021,10 +4021,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128790219</v>
+        <v>128790231</v>
       </c>
       <c r="B35" t="n">
-        <v>91494</v>
+        <v>57876</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4032,21 +4032,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4056,10 +4056,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>622240</v>
+        <v>622564</v>
       </c>
       <c r="R35" t="n">
-        <v>6974241</v>
+        <v>6973544</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4092,6 +4092,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4118,10 +4123,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128790231</v>
+        <v>128790219</v>
       </c>
       <c r="B36" t="n">
-        <v>57876</v>
+        <v>91494</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4129,21 +4134,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4153,10 +4158,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>622564</v>
+        <v>622240</v>
       </c>
       <c r="R36" t="n">
-        <v>6973544</v>
+        <v>6974241</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4189,11 +4194,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4419,10 +4419,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128790247</v>
+        <v>128790221</v>
       </c>
       <c r="B39" t="n">
-        <v>79116</v>
+        <v>91494</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4430,21 +4430,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>622267</v>
+        <v>622221</v>
       </c>
       <c r="R39" t="n">
-        <v>6974268</v>
+        <v>6974149</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4618,10 +4618,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128790221</v>
+        <v>128790247</v>
       </c>
       <c r="B41" t="n">
-        <v>91494</v>
+        <v>79116</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4629,21 +4629,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4653,10 +4653,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>622221</v>
+        <v>622267</v>
       </c>
       <c r="R41" t="n">
-        <v>6974149</v>
+        <v>6974268</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 26084-2025 artfynd.xlsx
+++ b/artfynd/A 26084-2025 artfynd.xlsx
@@ -1462,7 +1462,7 @@
         <v>128790214</v>
       </c>
       <c r="B9" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>128790237</v>
       </c>
       <c r="B10" t="n">
-        <v>91790</v>
+        <v>91795</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>128790218</v>
       </c>
       <c r="B11" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>128790241</v>
       </c>
       <c r="B13" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>128790244</v>
       </c>
       <c r="B15" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>128790234</v>
       </c>
       <c r="B17" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>128790217</v>
       </c>
       <c r="B18" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>128790238</v>
       </c>
       <c r="B19" t="n">
-        <v>91790</v>
+        <v>91795</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>128790235</v>
       </c>
       <c r="B20" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>128790220</v>
       </c>
       <c r="B21" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>128790245</v>
       </c>
       <c r="B23" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128790246</v>
+        <v>128790239</v>
       </c>
       <c r="B26" t="n">
-        <v>79116</v>
+        <v>80225</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3144,21 +3144,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>622548</v>
+        <v>622436</v>
       </c>
       <c r="R26" t="n">
-        <v>6973896</v>
+        <v>6973957</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3230,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128790239</v>
+        <v>128790246</v>
       </c>
       <c r="B27" t="n">
-        <v>80221</v>
+        <v>79120</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3241,21 +3241,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>622436</v>
+        <v>622548</v>
       </c>
       <c r="R27" t="n">
-        <v>6973957</v>
+        <v>6973896</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128790216</v>
+        <v>128790240</v>
       </c>
       <c r="B28" t="n">
-        <v>91494</v>
+        <v>80225</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3338,21 +3338,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>622450</v>
+        <v>622574</v>
       </c>
       <c r="R28" t="n">
-        <v>6974017</v>
+        <v>6973694</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3424,10 +3424,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128790240</v>
+        <v>128790216</v>
       </c>
       <c r="B29" t="n">
-        <v>80221</v>
+        <v>91499</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3435,21 +3435,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3459,10 +3459,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>622574</v>
+        <v>622450</v>
       </c>
       <c r="R29" t="n">
-        <v>6973694</v>
+        <v>6974017</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3626,7 +3626,7 @@
         <v>128790222</v>
       </c>
       <c r="B31" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>128790248</v>
       </c>
       <c r="B32" t="n">
-        <v>80256</v>
+        <v>80260</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4021,10 +4021,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128790231</v>
+        <v>128790219</v>
       </c>
       <c r="B35" t="n">
-        <v>57876</v>
+        <v>91499</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4032,21 +4032,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4056,10 +4056,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>622564</v>
+        <v>622240</v>
       </c>
       <c r="R35" t="n">
-        <v>6973544</v>
+        <v>6974241</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4092,11 +4092,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4123,10 +4118,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128790219</v>
+        <v>128790231</v>
       </c>
       <c r="B36" t="n">
-        <v>91494</v>
+        <v>57876</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4134,21 +4129,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4158,10 +4153,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>622240</v>
+        <v>622564</v>
       </c>
       <c r="R36" t="n">
-        <v>6974241</v>
+        <v>6973544</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4194,6 +4189,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4223,7 +4223,7 @@
         <v>128790213</v>
       </c>
       <c r="B37" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>128790221</v>
       </c>
       <c r="B39" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4516,10 +4516,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128790227</v>
+        <v>128790247</v>
       </c>
       <c r="B40" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4527,21 +4527,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4551,10 +4551,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>622646</v>
+        <v>622267</v>
       </c>
       <c r="R40" t="n">
-        <v>6973525</v>
+        <v>6974268</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4587,11 +4587,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4618,10 +4613,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128790247</v>
+        <v>128790227</v>
       </c>
       <c r="B41" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4629,21 +4624,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4653,10 +4648,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>622267</v>
+        <v>622646</v>
       </c>
       <c r="R41" t="n">
-        <v>6974268</v>
+        <v>6973525</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4689,6 +4684,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 26084-2025 artfynd.xlsx
+++ b/artfynd/A 26084-2025 artfynd.xlsx
@@ -1462,7 +1462,7 @@
         <v>128790214</v>
       </c>
       <c r="B9" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>128790237</v>
       </c>
       <c r="B10" t="n">
-        <v>91795</v>
+        <v>91800</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>128790218</v>
       </c>
       <c r="B11" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>128790244</v>
       </c>
       <c r="B15" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2245,32 +2245,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128790234</v>
+        <v>128790217</v>
       </c>
       <c r="B17" t="n">
-        <v>80254</v>
+        <v>91504</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>622437</v>
+        <v>622309</v>
       </c>
       <c r="R17" t="n">
-        <v>6973961</v>
+        <v>6974038</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2342,10 +2342,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128790217</v>
+        <v>128790238</v>
       </c>
       <c r="B18" t="n">
-        <v>91499</v>
+        <v>91800</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2353,21 +2353,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>622309</v>
+        <v>622403</v>
       </c>
       <c r="R18" t="n">
-        <v>6974038</v>
+        <v>6974067</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2439,32 +2439,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128790238</v>
+        <v>128790234</v>
       </c>
       <c r="B19" t="n">
-        <v>91795</v>
+        <v>80254</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>622403</v>
+        <v>622437</v>
       </c>
       <c r="R19" t="n">
-        <v>6974067</v>
+        <v>6973961</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2636,7 +2636,7 @@
         <v>128790220</v>
       </c>
       <c r="B21" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128790239</v>
+        <v>128790246</v>
       </c>
       <c r="B26" t="n">
-        <v>80225</v>
+        <v>79120</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3144,21 +3144,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>622436</v>
+        <v>622548</v>
       </c>
       <c r="R26" t="n">
-        <v>6973957</v>
+        <v>6973896</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3230,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128790246</v>
+        <v>128790239</v>
       </c>
       <c r="B27" t="n">
-        <v>79120</v>
+        <v>80225</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3241,21 +3241,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>622548</v>
+        <v>622436</v>
       </c>
       <c r="R27" t="n">
-        <v>6973896</v>
+        <v>6973957</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3427,7 +3427,7 @@
         <v>128790216</v>
       </c>
       <c r="B29" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>128790222</v>
       </c>
       <c r="B31" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         <v>128790219</v>
       </c>
       <c r="B35" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>128790213</v>
       </c>
       <c r="B37" t="n">
-        <v>91464</v>
+        <v>91469</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>128790221</v>
       </c>
       <c r="B39" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 26084-2025 artfynd.xlsx
+++ b/artfynd/A 26084-2025 artfynd.xlsx
@@ -2051,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128790244</v>
+        <v>128790232</v>
       </c>
       <c r="B15" t="n">
-        <v>91522</v>
+        <v>57876</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2062,21 +2062,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>622463</v>
+        <v>622266</v>
       </c>
       <c r="R15" t="n">
-        <v>6973956</v>
+        <v>6974205</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,10 +2148,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128790232</v>
+        <v>128790244</v>
       </c>
       <c r="B16" t="n">
-        <v>57876</v>
+        <v>91522</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2159,21 +2159,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>622266</v>
+        <v>622463</v>
       </c>
       <c r="R16" t="n">
-        <v>6974205</v>
+        <v>6973956</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128790240</v>
+        <v>128790216</v>
       </c>
       <c r="B28" t="n">
-        <v>80225</v>
+        <v>91504</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3338,21 +3338,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>622574</v>
+        <v>622450</v>
       </c>
       <c r="R28" t="n">
-        <v>6973694</v>
+        <v>6974017</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3424,10 +3424,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128790216</v>
+        <v>128790240</v>
       </c>
       <c r="B29" t="n">
-        <v>91504</v>
+        <v>80225</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3435,21 +3435,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3459,10 +3459,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>622450</v>
+        <v>622574</v>
       </c>
       <c r="R29" t="n">
-        <v>6974017</v>
+        <v>6973694</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3817,7 +3817,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128790223</v>
+        <v>128790229</v>
       </c>
       <c r="B33" t="n">
         <v>57716</v>
@@ -3852,10 +3852,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>622582</v>
+        <v>622639</v>
       </c>
       <c r="R33" t="n">
-        <v>6973719</v>
+        <v>6973634</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3919,7 +3919,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128790229</v>
+        <v>128790223</v>
       </c>
       <c r="B34" t="n">
         <v>57716</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>622639</v>
+        <v>622582</v>
       </c>
       <c r="R34" t="n">
-        <v>6973634</v>
+        <v>6973719</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4419,10 +4419,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128790221</v>
+        <v>128790247</v>
       </c>
       <c r="B39" t="n">
-        <v>91504</v>
+        <v>79120</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4430,21 +4430,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>622221</v>
+        <v>622267</v>
       </c>
       <c r="R39" t="n">
-        <v>6974149</v>
+        <v>6974268</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4516,10 +4516,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128790247</v>
+        <v>128790221</v>
       </c>
       <c r="B40" t="n">
-        <v>79120</v>
+        <v>91504</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4527,21 +4527,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4551,10 +4551,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>622267</v>
+        <v>622221</v>
       </c>
       <c r="R40" t="n">
-        <v>6974268</v>
+        <v>6974149</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>

--- a/artfynd/A 26084-2025 artfynd.xlsx
+++ b/artfynd/A 26084-2025 artfynd.xlsx
@@ -2051,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128790232</v>
+        <v>128790244</v>
       </c>
       <c r="B15" t="n">
-        <v>57876</v>
+        <v>91522</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2062,21 +2062,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>622266</v>
+        <v>622463</v>
       </c>
       <c r="R15" t="n">
-        <v>6974205</v>
+        <v>6973956</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,10 +2148,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128790244</v>
+        <v>128790232</v>
       </c>
       <c r="B16" t="n">
-        <v>91522</v>
+        <v>57876</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2159,21 +2159,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>622463</v>
+        <v>622266</v>
       </c>
       <c r="R16" t="n">
-        <v>6973956</v>
+        <v>6974205</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2245,10 +2245,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128790217</v>
+        <v>128790238</v>
       </c>
       <c r="B17" t="n">
-        <v>91504</v>
+        <v>91800</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2256,21 +2256,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>622309</v>
+        <v>622403</v>
       </c>
       <c r="R17" t="n">
-        <v>6974038</v>
+        <v>6974067</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2342,32 +2342,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128790238</v>
+        <v>128790234</v>
       </c>
       <c r="B18" t="n">
-        <v>91800</v>
+        <v>80254</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>622403</v>
+        <v>622437</v>
       </c>
       <c r="R18" t="n">
-        <v>6974067</v>
+        <v>6973961</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2439,32 +2439,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128790234</v>
+        <v>128790217</v>
       </c>
       <c r="B19" t="n">
-        <v>80254</v>
+        <v>91504</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>622437</v>
+        <v>622309</v>
       </c>
       <c r="R19" t="n">
-        <v>6973961</v>
+        <v>6974038</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128790246</v>
+        <v>128790239</v>
       </c>
       <c r="B26" t="n">
-        <v>79120</v>
+        <v>80225</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3144,21 +3144,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>622548</v>
+        <v>622436</v>
       </c>
       <c r="R26" t="n">
-        <v>6973896</v>
+        <v>6973957</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3230,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128790239</v>
+        <v>128790246</v>
       </c>
       <c r="B27" t="n">
-        <v>80225</v>
+        <v>79120</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3241,21 +3241,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>622436</v>
+        <v>622548</v>
       </c>
       <c r="R27" t="n">
-        <v>6973957</v>
+        <v>6973896</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4419,10 +4419,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128790247</v>
+        <v>128790221</v>
       </c>
       <c r="B39" t="n">
-        <v>79120</v>
+        <v>91504</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4430,21 +4430,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>622267</v>
+        <v>622221</v>
       </c>
       <c r="R39" t="n">
-        <v>6974268</v>
+        <v>6974149</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4516,10 +4516,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128790221</v>
+        <v>128790247</v>
       </c>
       <c r="B40" t="n">
-        <v>91504</v>
+        <v>79120</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4527,21 +4527,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4551,10 +4551,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>622221</v>
+        <v>622267</v>
       </c>
       <c r="R40" t="n">
-        <v>6974149</v>
+        <v>6974268</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>

--- a/artfynd/A 26084-2025 artfynd.xlsx
+++ b/artfynd/A 26084-2025 artfynd.xlsx
@@ -1462,7 +1462,7 @@
         <v>128790214</v>
       </c>
       <c r="B9" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128790237</v>
+        <v>128790218</v>
       </c>
       <c r="B10" t="n">
-        <v>91800</v>
+        <v>91508</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1567,21 +1567,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>622211</v>
+        <v>622266</v>
       </c>
       <c r="R10" t="n">
-        <v>6974148</v>
+        <v>6974203</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128790218</v>
+        <v>128790237</v>
       </c>
       <c r="B11" t="n">
-        <v>91504</v>
+        <v>91804</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,21 +1664,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>622266</v>
+        <v>622211</v>
       </c>
       <c r="R11" t="n">
-        <v>6974203</v>
+        <v>6974148</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,7 +1753,7 @@
         <v>128790233</v>
       </c>
       <c r="B12" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>128790241</v>
       </c>
       <c r="B13" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>128790230</v>
       </c>
       <c r="B14" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>128790244</v>
       </c>
       <c r="B15" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>128790232</v>
       </c>
       <c r="B16" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2245,10 +2245,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128790238</v>
+        <v>128790217</v>
       </c>
       <c r="B17" t="n">
-        <v>91800</v>
+        <v>91508</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2256,21 +2256,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>622403</v>
+        <v>622309</v>
       </c>
       <c r="R17" t="n">
-        <v>6974067</v>
+        <v>6974038</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2342,32 +2342,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128790234</v>
+        <v>128790238</v>
       </c>
       <c r="B18" t="n">
-        <v>80254</v>
+        <v>91804</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>622437</v>
+        <v>622403</v>
       </c>
       <c r="R18" t="n">
-        <v>6973961</v>
+        <v>6974067</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2439,32 +2439,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128790217</v>
+        <v>128790234</v>
       </c>
       <c r="B19" t="n">
-        <v>91504</v>
+        <v>80258</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>622309</v>
+        <v>622437</v>
       </c>
       <c r="R19" t="n">
-        <v>6974038</v>
+        <v>6973961</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2539,7 +2539,7 @@
         <v>128790235</v>
       </c>
       <c r="B20" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>128790220</v>
       </c>
       <c r="B21" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>128790224</v>
       </c>
       <c r="B22" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>128790245</v>
       </c>
       <c r="B23" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>128790228</v>
       </c>
       <c r="B24" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>128790225</v>
       </c>
       <c r="B25" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128790239</v>
+        <v>128790246</v>
       </c>
       <c r="B26" t="n">
-        <v>80225</v>
+        <v>79124</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3144,21 +3144,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>622436</v>
+        <v>622548</v>
       </c>
       <c r="R26" t="n">
-        <v>6973957</v>
+        <v>6973896</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3230,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128790246</v>
+        <v>128790239</v>
       </c>
       <c r="B27" t="n">
-        <v>79120</v>
+        <v>80229</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3241,21 +3241,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>622548</v>
+        <v>622436</v>
       </c>
       <c r="R27" t="n">
-        <v>6973896</v>
+        <v>6973957</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3330,7 +3330,7 @@
         <v>128790216</v>
       </c>
       <c r="B28" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>128790240</v>
       </c>
       <c r="B29" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>128790226</v>
       </c>
       <c r="B30" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>128790222</v>
       </c>
       <c r="B31" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>128790248</v>
       </c>
       <c r="B32" t="n">
-        <v>80260</v>
+        <v>80264</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3817,10 +3817,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128790229</v>
+        <v>128790223</v>
       </c>
       <c r="B33" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3852,10 +3852,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>622639</v>
+        <v>622582</v>
       </c>
       <c r="R33" t="n">
-        <v>6973634</v>
+        <v>6973719</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3919,10 +3919,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128790223</v>
+        <v>128790229</v>
       </c>
       <c r="B34" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>622582</v>
+        <v>622639</v>
       </c>
       <c r="R34" t="n">
-        <v>6973719</v>
+        <v>6973634</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4024,7 +4024,7 @@
         <v>128790219</v>
       </c>
       <c r="B35" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         <v>128790231</v>
       </c>
       <c r="B36" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>128790213</v>
       </c>
       <c r="B37" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>128790236</v>
       </c>
       <c r="B38" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4419,10 +4419,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128790221</v>
+        <v>128790247</v>
       </c>
       <c r="B39" t="n">
-        <v>91504</v>
+        <v>79124</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4430,21 +4430,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>622221</v>
+        <v>622267</v>
       </c>
       <c r="R39" t="n">
-        <v>6974149</v>
+        <v>6974268</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4516,10 +4516,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128790247</v>
+        <v>128790227</v>
       </c>
       <c r="B40" t="n">
-        <v>79120</v>
+        <v>57720</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4527,21 +4527,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4551,10 +4551,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>622267</v>
+        <v>622646</v>
       </c>
       <c r="R40" t="n">
-        <v>6974268</v>
+        <v>6973525</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4587,6 +4587,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4613,10 +4618,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128790227</v>
+        <v>128790221</v>
       </c>
       <c r="B41" t="n">
-        <v>57716</v>
+        <v>91508</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4624,21 +4629,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4648,10 +4653,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>622646</v>
+        <v>622221</v>
       </c>
       <c r="R41" t="n">
-        <v>6973525</v>
+        <v>6974149</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4684,11 +4689,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 26084-2025 artfynd.xlsx
+++ b/artfynd/A 26084-2025 artfynd.xlsx
@@ -1556,10 +1556,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128790218</v>
+        <v>128790233</v>
       </c>
       <c r="B10" t="n">
-        <v>91508</v>
+        <v>57880</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1567,21 +1567,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>622266</v>
+        <v>622221</v>
       </c>
       <c r="R10" t="n">
-        <v>6974203</v>
+        <v>6974121</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,6 +1627,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1750,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128790233</v>
+        <v>128790218</v>
       </c>
       <c r="B12" t="n">
-        <v>57880</v>
+        <v>91508</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1761,21 +1766,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>622221</v>
+        <v>622266</v>
       </c>
       <c r="R12" t="n">
-        <v>6974121</v>
+        <v>6974203</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1821,11 +1826,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2051,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128790244</v>
+        <v>128790232</v>
       </c>
       <c r="B15" t="n">
-        <v>91526</v>
+        <v>57880</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2062,21 +2062,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>622463</v>
+        <v>622266</v>
       </c>
       <c r="R15" t="n">
-        <v>6973956</v>
+        <v>6974205</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,10 +2148,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128790232</v>
+        <v>128790244</v>
       </c>
       <c r="B16" t="n">
-        <v>57880</v>
+        <v>91526</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2159,21 +2159,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>622266</v>
+        <v>622463</v>
       </c>
       <c r="R16" t="n">
-        <v>6974205</v>
+        <v>6973956</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2832,10 +2832,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128790245</v>
+        <v>128790228</v>
       </c>
       <c r="B23" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2843,21 +2843,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2867,10 +2867,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>622540</v>
+        <v>622637</v>
       </c>
       <c r="R23" t="n">
-        <v>6973635</v>
+        <v>6973628</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2903,6 +2903,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2929,10 +2934,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128790228</v>
+        <v>128790245</v>
       </c>
       <c r="B24" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2940,21 +2945,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2964,10 +2969,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>622637</v>
+        <v>622540</v>
       </c>
       <c r="R24" t="n">
-        <v>6973628</v>
+        <v>6973635</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3000,11 +3005,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3133,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128790246</v>
+        <v>128790239</v>
       </c>
       <c r="B26" t="n">
-        <v>79124</v>
+        <v>80229</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3144,21 +3144,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>622548</v>
+        <v>622436</v>
       </c>
       <c r="R26" t="n">
-        <v>6973896</v>
+        <v>6973957</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3230,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128790239</v>
+        <v>128790246</v>
       </c>
       <c r="B27" t="n">
-        <v>80229</v>
+        <v>79124</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3241,21 +3241,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>622436</v>
+        <v>622548</v>
       </c>
       <c r="R27" t="n">
-        <v>6973957</v>
+        <v>6973896</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4419,10 +4419,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128790247</v>
+        <v>128790221</v>
       </c>
       <c r="B39" t="n">
-        <v>79124</v>
+        <v>91508</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4430,21 +4430,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>622267</v>
+        <v>622221</v>
       </c>
       <c r="R39" t="n">
-        <v>6974268</v>
+        <v>6974149</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4516,10 +4516,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128790227</v>
+        <v>128790247</v>
       </c>
       <c r="B40" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4527,21 +4527,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4551,10 +4551,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>622646</v>
+        <v>622267</v>
       </c>
       <c r="R40" t="n">
-        <v>6973525</v>
+        <v>6974268</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4587,11 +4587,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4618,10 +4613,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128790221</v>
+        <v>128790227</v>
       </c>
       <c r="B41" t="n">
-        <v>91508</v>
+        <v>57720</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4629,21 +4624,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4653,10 +4648,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>622221</v>
+        <v>622646</v>
       </c>
       <c r="R41" t="n">
-        <v>6974149</v>
+        <v>6973525</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4689,6 +4684,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 26084-2025 artfynd.xlsx
+++ b/artfynd/A 26084-2025 artfynd.xlsx
@@ -1556,10 +1556,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128790233</v>
+        <v>128790237</v>
       </c>
       <c r="B10" t="n">
-        <v>57880</v>
+        <v>91804</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1567,21 +1567,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>622221</v>
+        <v>622211</v>
       </c>
       <c r="R10" t="n">
-        <v>6974121</v>
+        <v>6974148</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,11 +1627,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1658,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128790237</v>
+        <v>128790218</v>
       </c>
       <c r="B11" t="n">
-        <v>91804</v>
+        <v>91508</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,21 +1664,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1693,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>622211</v>
+        <v>622266</v>
       </c>
       <c r="R11" t="n">
-        <v>6974148</v>
+        <v>6974203</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1755,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128790218</v>
+        <v>128790233</v>
       </c>
       <c r="B12" t="n">
-        <v>91508</v>
+        <v>57880</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,21 +1761,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>622266</v>
+        <v>622221</v>
       </c>
       <c r="R12" t="n">
-        <v>6974203</v>
+        <v>6974121</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1826,6 +1821,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2051,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128790232</v>
+        <v>128790244</v>
       </c>
       <c r="B15" t="n">
-        <v>57880</v>
+        <v>91526</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2062,21 +2062,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>622266</v>
+        <v>622463</v>
       </c>
       <c r="R15" t="n">
-        <v>6974205</v>
+        <v>6973956</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,10 +2148,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128790244</v>
+        <v>128790232</v>
       </c>
       <c r="B16" t="n">
-        <v>91526</v>
+        <v>57880</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2159,21 +2159,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>622463</v>
+        <v>622266</v>
       </c>
       <c r="R16" t="n">
-        <v>6973956</v>
+        <v>6974205</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2832,10 +2832,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128790228</v>
+        <v>128790245</v>
       </c>
       <c r="B23" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2843,21 +2843,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2867,10 +2867,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>622637</v>
+        <v>622540</v>
       </c>
       <c r="R23" t="n">
-        <v>6973628</v>
+        <v>6973635</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2903,11 +2903,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2934,10 +2929,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128790245</v>
+        <v>128790228</v>
       </c>
       <c r="B24" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2945,21 +2940,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2969,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>622540</v>
+        <v>622637</v>
       </c>
       <c r="R24" t="n">
-        <v>6973635</v>
+        <v>6973628</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3005,6 +3000,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3133,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128790239</v>
+        <v>128790246</v>
       </c>
       <c r="B26" t="n">
-        <v>80229</v>
+        <v>79124</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3144,21 +3144,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>622436</v>
+        <v>622548</v>
       </c>
       <c r="R26" t="n">
-        <v>6973957</v>
+        <v>6973896</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3230,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128790246</v>
+        <v>128790239</v>
       </c>
       <c r="B27" t="n">
-        <v>79124</v>
+        <v>80229</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3241,21 +3241,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>622548</v>
+        <v>622436</v>
       </c>
       <c r="R27" t="n">
-        <v>6973896</v>
+        <v>6973957</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 26084-2025 artfynd.xlsx
+++ b/artfynd/A 26084-2025 artfynd.xlsx
@@ -1462,7 +1462,7 @@
         <v>128790214</v>
       </c>
       <c r="B9" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>128790237</v>
       </c>
       <c r="B10" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>128790218</v>
       </c>
       <c r="B11" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>128790233</v>
       </c>
       <c r="B12" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128790241</v>
+        <v>128790230</v>
       </c>
       <c r="B13" t="n">
-        <v>80229</v>
+        <v>57723</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>622266</v>
+        <v>622493</v>
       </c>
       <c r="R13" t="n">
-        <v>6974089</v>
+        <v>6973939</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1923,6 +1923,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128790230</v>
+        <v>128790241</v>
       </c>
       <c r="B14" t="n">
-        <v>57720</v>
+        <v>80134</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1960,21 +1965,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>622493</v>
+        <v>622266</v>
       </c>
       <c r="R14" t="n">
-        <v>6973939</v>
+        <v>6974089</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2020,11 +2025,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2054,7 +2054,7 @@
         <v>128790244</v>
       </c>
       <c r="B15" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>128790232</v>
       </c>
       <c r="B16" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2245,32 +2245,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128790217</v>
+        <v>128790234</v>
       </c>
       <c r="B17" t="n">
-        <v>91508</v>
+        <v>80163</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>622309</v>
+        <v>622437</v>
       </c>
       <c r="R17" t="n">
-        <v>6974038</v>
+        <v>6973961</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2342,10 +2342,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128790238</v>
+        <v>128790217</v>
       </c>
       <c r="B18" t="n">
-        <v>91804</v>
+        <v>91513</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2353,21 +2353,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>622403</v>
+        <v>622309</v>
       </c>
       <c r="R18" t="n">
-        <v>6974067</v>
+        <v>6974038</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2439,32 +2439,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128790234</v>
+        <v>128790238</v>
       </c>
       <c r="B19" t="n">
-        <v>80258</v>
+        <v>91809</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>622437</v>
+        <v>622403</v>
       </c>
       <c r="R19" t="n">
-        <v>6973961</v>
+        <v>6974067</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2539,7 +2539,7 @@
         <v>128790235</v>
       </c>
       <c r="B20" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>128790220</v>
       </c>
       <c r="B21" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>128790224</v>
       </c>
       <c r="B22" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>128790245</v>
       </c>
       <c r="B23" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>128790228</v>
       </c>
       <c r="B24" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>128790225</v>
       </c>
       <c r="B25" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128790246</v>
+        <v>128790239</v>
       </c>
       <c r="B26" t="n">
-        <v>79124</v>
+        <v>80134</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3144,21 +3144,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>622548</v>
+        <v>622436</v>
       </c>
       <c r="R26" t="n">
-        <v>6973896</v>
+        <v>6973957</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3230,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128790239</v>
+        <v>128790246</v>
       </c>
       <c r="B27" t="n">
-        <v>80229</v>
+        <v>79029</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3241,21 +3241,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>622436</v>
+        <v>622548</v>
       </c>
       <c r="R27" t="n">
-        <v>6973957</v>
+        <v>6973896</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128790216</v>
+        <v>128790240</v>
       </c>
       <c r="B28" t="n">
-        <v>91508</v>
+        <v>80134</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3338,21 +3338,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>622450</v>
+        <v>622574</v>
       </c>
       <c r="R28" t="n">
-        <v>6974017</v>
+        <v>6973694</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3424,10 +3424,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128790240</v>
+        <v>128790216</v>
       </c>
       <c r="B29" t="n">
-        <v>80229</v>
+        <v>91513</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3435,21 +3435,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3459,10 +3459,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>622574</v>
+        <v>622450</v>
       </c>
       <c r="R29" t="n">
-        <v>6973694</v>
+        <v>6974017</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3524,7 +3524,7 @@
         <v>128790226</v>
       </c>
       <c r="B30" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>128790222</v>
       </c>
       <c r="B31" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>128790248</v>
       </c>
       <c r="B32" t="n">
-        <v>80264</v>
+        <v>80169</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>128790223</v>
       </c>
       <c r="B33" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>128790229</v>
       </c>
       <c r="B34" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         <v>128790219</v>
       </c>
       <c r="B35" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         <v>128790231</v>
       </c>
       <c r="B36" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>128790213</v>
       </c>
       <c r="B37" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>128790236</v>
       </c>
       <c r="B38" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>128790221</v>
       </c>
       <c r="B39" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>128790247</v>
       </c>
       <c r="B40" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4616,7 +4616,7 @@
         <v>128790227</v>
       </c>
       <c r="B41" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 26084-2025 artfynd.xlsx
+++ b/artfynd/A 26084-2025 artfynd.xlsx
@@ -4419,10 +4419,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128790221</v>
+        <v>128790227</v>
       </c>
       <c r="B39" t="n">
-        <v>91520</v>
+        <v>57723</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4430,21 +4430,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>622221</v>
+        <v>622646</v>
       </c>
       <c r="R39" t="n">
-        <v>6974149</v>
+        <v>6973525</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4490,6 +4490,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4516,10 +4521,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128790227</v>
+        <v>128790247</v>
       </c>
       <c r="B40" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4527,21 +4532,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4551,10 +4556,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>622646</v>
+        <v>622267</v>
       </c>
       <c r="R40" t="n">
-        <v>6973525</v>
+        <v>6974268</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4587,11 +4592,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4618,10 +4618,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128790247</v>
+        <v>128790221</v>
       </c>
       <c r="B41" t="n">
-        <v>79034</v>
+        <v>91520</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4629,21 +4629,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4653,10 +4653,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>622267</v>
+        <v>622221</v>
       </c>
       <c r="R41" t="n">
-        <v>6974268</v>
+        <v>6974149</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 26084-2025 artfynd.xlsx
+++ b/artfynd/A 26084-2025 artfynd.xlsx
@@ -1462,7 +1462,7 @@
         <v>128790214</v>
       </c>
       <c r="B9" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>128790218</v>
       </c>
       <c r="B10" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1653,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128790233</v>
+        <v>128790237</v>
       </c>
       <c r="B11" t="n">
-        <v>57883</v>
+        <v>91808</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,21 +1664,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>622221</v>
+        <v>622211</v>
       </c>
       <c r="R11" t="n">
-        <v>6974121</v>
+        <v>6974148</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,11 +1724,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128790237</v>
+        <v>128790233</v>
       </c>
       <c r="B12" t="n">
-        <v>91805</v>
+        <v>57883</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,21 +1761,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>622211</v>
+        <v>622221</v>
       </c>
       <c r="R12" t="n">
-        <v>6974148</v>
+        <v>6974121</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1826,6 +1821,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2054,7 +2054,7 @@
         <v>128790244</v>
       </c>
       <c r="B15" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2245,10 +2245,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128790238</v>
+        <v>128790217</v>
       </c>
       <c r="B17" t="n">
-        <v>91805</v>
+        <v>91523</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2256,21 +2256,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>622403</v>
+        <v>622309</v>
       </c>
       <c r="R17" t="n">
-        <v>6974067</v>
+        <v>6974038</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2342,10 +2342,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128790217</v>
+        <v>128790238</v>
       </c>
       <c r="B18" t="n">
-        <v>91520</v>
+        <v>91808</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2353,21 +2353,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>622309</v>
+        <v>622403</v>
       </c>
       <c r="R18" t="n">
-        <v>6974038</v>
+        <v>6974067</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2636,7 +2636,7 @@
         <v>128790220</v>
       </c>
       <c r="B21" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>128790216</v>
       </c>
       <c r="B28" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>128790222</v>
       </c>
       <c r="B31" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4021,10 +4021,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128790231</v>
+        <v>128790219</v>
       </c>
       <c r="B35" t="n">
-        <v>57883</v>
+        <v>91523</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4032,21 +4032,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4056,10 +4056,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>622564</v>
+        <v>622240</v>
       </c>
       <c r="R35" t="n">
-        <v>6973544</v>
+        <v>6974241</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4092,11 +4092,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4123,10 +4118,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128790219</v>
+        <v>128790231</v>
       </c>
       <c r="B36" t="n">
-        <v>91520</v>
+        <v>57883</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4134,21 +4129,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4158,10 +4153,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>622240</v>
+        <v>622564</v>
       </c>
       <c r="R36" t="n">
-        <v>6974241</v>
+        <v>6973544</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4194,6 +4189,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4223,7 +4223,7 @@
         <v>128790213</v>
       </c>
       <c r="B37" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4419,10 +4419,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128790227</v>
+        <v>128790247</v>
       </c>
       <c r="B39" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4430,21 +4430,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>622646</v>
+        <v>622267</v>
       </c>
       <c r="R39" t="n">
-        <v>6973525</v>
+        <v>6974268</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4490,11 +4490,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4521,10 +4516,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128790247</v>
+        <v>128790221</v>
       </c>
       <c r="B40" t="n">
-        <v>79034</v>
+        <v>91523</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4532,21 +4527,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4556,10 +4551,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>622267</v>
+        <v>622221</v>
       </c>
       <c r="R40" t="n">
-        <v>6974268</v>
+        <v>6974149</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4618,10 +4613,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128790221</v>
+        <v>128790227</v>
       </c>
       <c r="B41" t="n">
-        <v>91520</v>
+        <v>57723</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4629,21 +4624,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4653,10 +4648,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>622221</v>
+        <v>622646</v>
       </c>
       <c r="R41" t="n">
-        <v>6974149</v>
+        <v>6973525</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4689,6 +4684,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 26084-2025 artfynd.xlsx
+++ b/artfynd/A 26084-2025 artfynd.xlsx
@@ -1462,7 +1462,7 @@
         <v>128790214</v>
       </c>
       <c r="B9" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128790218</v>
+        <v>128790233</v>
       </c>
       <c r="B10" t="n">
-        <v>91523</v>
+        <v>57883</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1567,21 +1567,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>622266</v>
+        <v>622221</v>
       </c>
       <c r="R10" t="n">
-        <v>6974203</v>
+        <v>6974121</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,6 +1627,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128790237</v>
+        <v>128790218</v>
       </c>
       <c r="B11" t="n">
-        <v>91808</v>
+        <v>91526</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,21 +1669,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1688,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>622211</v>
+        <v>622266</v>
       </c>
       <c r="R11" t="n">
-        <v>6974148</v>
+        <v>6974203</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1750,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128790233</v>
+        <v>128790237</v>
       </c>
       <c r="B12" t="n">
-        <v>57883</v>
+        <v>91811</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1761,21 +1766,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>622221</v>
+        <v>622211</v>
       </c>
       <c r="R12" t="n">
-        <v>6974121</v>
+        <v>6974148</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1821,11 +1826,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1855,7 +1855,7 @@
         <v>128790241</v>
       </c>
       <c r="B13" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2051,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128790244</v>
+        <v>128790232</v>
       </c>
       <c r="B15" t="n">
-        <v>91541</v>
+        <v>57883</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2062,21 +2062,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>622463</v>
+        <v>622266</v>
       </c>
       <c r="R15" t="n">
-        <v>6973956</v>
+        <v>6974205</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,10 +2148,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128790232</v>
+        <v>128790244</v>
       </c>
       <c r="B16" t="n">
-        <v>57883</v>
+        <v>91544</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2159,21 +2159,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>622266</v>
+        <v>622463</v>
       </c>
       <c r="R16" t="n">
-        <v>6974205</v>
+        <v>6973956</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2245,32 +2245,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128790217</v>
+        <v>128790234</v>
       </c>
       <c r="B17" t="n">
-        <v>91523</v>
+        <v>80169</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>622309</v>
+        <v>622437</v>
       </c>
       <c r="R17" t="n">
-        <v>6974038</v>
+        <v>6973961</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2342,10 +2342,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128790238</v>
+        <v>128790217</v>
       </c>
       <c r="B18" t="n">
-        <v>91808</v>
+        <v>91526</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2353,21 +2353,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>622403</v>
+        <v>622309</v>
       </c>
       <c r="R18" t="n">
-        <v>6974067</v>
+        <v>6974038</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2439,32 +2439,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128790234</v>
+        <v>128790238</v>
       </c>
       <c r="B19" t="n">
-        <v>80168</v>
+        <v>91811</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>622437</v>
+        <v>622403</v>
       </c>
       <c r="R19" t="n">
-        <v>6973961</v>
+        <v>6974067</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2539,7 +2539,7 @@
         <v>128790235</v>
       </c>
       <c r="B20" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>128790220</v>
       </c>
       <c r="B21" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2832,10 +2832,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128790228</v>
+        <v>128790245</v>
       </c>
       <c r="B23" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2843,21 +2843,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2867,10 +2867,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>622637</v>
+        <v>622540</v>
       </c>
       <c r="R23" t="n">
-        <v>6973628</v>
+        <v>6973635</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2903,11 +2903,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2934,10 +2929,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128790245</v>
+        <v>128790228</v>
       </c>
       <c r="B24" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2945,21 +2940,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2969,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>622540</v>
+        <v>622637</v>
       </c>
       <c r="R24" t="n">
-        <v>6973635</v>
+        <v>6973628</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3005,6 +3000,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3136,7 +3136,7 @@
         <v>128790246</v>
       </c>
       <c r="B26" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>128790239</v>
       </c>
       <c r="B27" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>128790216</v>
       </c>
       <c r="B28" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>128790240</v>
       </c>
       <c r="B29" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>128790222</v>
       </c>
       <c r="B31" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>128790248</v>
       </c>
       <c r="B32" t="n">
-        <v>80174</v>
+        <v>80175</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4021,10 +4021,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128790219</v>
+        <v>128790231</v>
       </c>
       <c r="B35" t="n">
-        <v>91523</v>
+        <v>57883</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4032,21 +4032,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4056,10 +4056,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>622240</v>
+        <v>622564</v>
       </c>
       <c r="R35" t="n">
-        <v>6974241</v>
+        <v>6973544</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4092,6 +4092,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4118,10 +4123,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128790231</v>
+        <v>128790219</v>
       </c>
       <c r="B36" t="n">
-        <v>57883</v>
+        <v>91526</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4129,21 +4134,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4153,10 +4158,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>622564</v>
+        <v>622240</v>
       </c>
       <c r="R36" t="n">
-        <v>6973544</v>
+        <v>6974241</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4189,11 +4194,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4223,7 +4223,7 @@
         <v>128790213</v>
       </c>
       <c r="B37" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>128790247</v>
       </c>
       <c r="B39" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4516,10 +4516,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128790221</v>
+        <v>128790227</v>
       </c>
       <c r="B40" t="n">
-        <v>91523</v>
+        <v>57723</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4527,21 +4527,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4551,10 +4551,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>622221</v>
+        <v>622646</v>
       </c>
       <c r="R40" t="n">
-        <v>6974149</v>
+        <v>6973525</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4587,6 +4587,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4613,10 +4618,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128790227</v>
+        <v>128790221</v>
       </c>
       <c r="B41" t="n">
-        <v>57723</v>
+        <v>91526</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4624,21 +4629,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4648,10 +4653,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>622646</v>
+        <v>622221</v>
       </c>
       <c r="R41" t="n">
-        <v>6973525</v>
+        <v>6974149</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4684,11 +4689,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 26084-2025 artfynd.xlsx
+++ b/artfynd/A 26084-2025 artfynd.xlsx
@@ -1556,10 +1556,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128790233</v>
+        <v>128790237</v>
       </c>
       <c r="B10" t="n">
-        <v>57883</v>
+        <v>91811</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1567,21 +1567,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>622221</v>
+        <v>622211</v>
       </c>
       <c r="R10" t="n">
-        <v>6974121</v>
+        <v>6974148</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,11 +1627,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1755,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128790237</v>
+        <v>128790233</v>
       </c>
       <c r="B12" t="n">
-        <v>91811</v>
+        <v>57883</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,21 +1761,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>622211</v>
+        <v>622221</v>
       </c>
       <c r="R12" t="n">
-        <v>6974148</v>
+        <v>6974121</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1826,6 +1821,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2051,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128790232</v>
+        <v>128790244</v>
       </c>
       <c r="B15" t="n">
-        <v>57883</v>
+        <v>91544</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2062,21 +2062,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>622266</v>
+        <v>622463</v>
       </c>
       <c r="R15" t="n">
-        <v>6974205</v>
+        <v>6973956</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,10 +2148,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128790244</v>
+        <v>128790232</v>
       </c>
       <c r="B16" t="n">
-        <v>91544</v>
+        <v>57883</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2159,21 +2159,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>622463</v>
+        <v>622266</v>
       </c>
       <c r="R16" t="n">
-        <v>6973956</v>
+        <v>6974205</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2245,32 +2245,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128790234</v>
+        <v>128790238</v>
       </c>
       <c r="B17" t="n">
-        <v>80169</v>
+        <v>91811</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>622437</v>
+        <v>622403</v>
       </c>
       <c r="R17" t="n">
-        <v>6973961</v>
+        <v>6974067</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2439,32 +2439,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128790238</v>
+        <v>128790234</v>
       </c>
       <c r="B19" t="n">
-        <v>91811</v>
+        <v>80169</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>622403</v>
+        <v>622437</v>
       </c>
       <c r="R19" t="n">
-        <v>6974067</v>
+        <v>6973961</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -4021,10 +4021,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128790231</v>
+        <v>128790219</v>
       </c>
       <c r="B35" t="n">
-        <v>57883</v>
+        <v>91526</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4032,21 +4032,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4056,10 +4056,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>622564</v>
+        <v>622240</v>
       </c>
       <c r="R35" t="n">
-        <v>6973544</v>
+        <v>6974241</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4092,11 +4092,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4123,10 +4118,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128790219</v>
+        <v>128790231</v>
       </c>
       <c r="B36" t="n">
-        <v>91526</v>
+        <v>57883</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4134,21 +4129,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4158,10 +4153,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>622240</v>
+        <v>622564</v>
       </c>
       <c r="R36" t="n">
-        <v>6974241</v>
+        <v>6973544</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4194,6 +4189,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4419,10 +4419,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128790247</v>
+        <v>128790221</v>
       </c>
       <c r="B39" t="n">
-        <v>79035</v>
+        <v>91526</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4430,21 +4430,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>622267</v>
+        <v>622221</v>
       </c>
       <c r="R39" t="n">
-        <v>6974268</v>
+        <v>6974149</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4516,10 +4516,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128790227</v>
+        <v>128790247</v>
       </c>
       <c r="B40" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4527,21 +4527,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4551,10 +4551,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>622646</v>
+        <v>622267</v>
       </c>
       <c r="R40" t="n">
-        <v>6973525</v>
+        <v>6974268</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4587,11 +4587,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4618,10 +4613,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128790221</v>
+        <v>128790227</v>
       </c>
       <c r="B41" t="n">
-        <v>91526</v>
+        <v>57723</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4629,21 +4624,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4653,10 +4648,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>622221</v>
+        <v>622646</v>
       </c>
       <c r="R41" t="n">
-        <v>6974149</v>
+        <v>6973525</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4689,6 +4684,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 26084-2025 artfynd.xlsx
+++ b/artfynd/A 26084-2025 artfynd.xlsx
@@ -1556,10 +1556,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128790237</v>
+        <v>128790233</v>
       </c>
       <c r="B10" t="n">
-        <v>91811</v>
+        <v>57883</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1567,21 +1567,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>622211</v>
+        <v>622221</v>
       </c>
       <c r="R10" t="n">
-        <v>6974148</v>
+        <v>6974121</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,6 +1627,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128790218</v>
+        <v>128790237</v>
       </c>
       <c r="B11" t="n">
-        <v>91526</v>
+        <v>91811</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,21 +1669,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1688,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>622266</v>
+        <v>622211</v>
       </c>
       <c r="R11" t="n">
-        <v>6974203</v>
+        <v>6974148</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1750,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128790233</v>
+        <v>128790218</v>
       </c>
       <c r="B12" t="n">
-        <v>57883</v>
+        <v>91526</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1761,21 +1766,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>622221</v>
+        <v>622266</v>
       </c>
       <c r="R12" t="n">
-        <v>6974121</v>
+        <v>6974203</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1821,11 +1826,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128790241</v>
+        <v>128790230</v>
       </c>
       <c r="B13" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>622266</v>
+        <v>622493</v>
       </c>
       <c r="R13" t="n">
-        <v>6974089</v>
+        <v>6973939</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1923,6 +1923,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128790230</v>
+        <v>128790241</v>
       </c>
       <c r="B14" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1960,21 +1965,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>622493</v>
+        <v>622266</v>
       </c>
       <c r="R14" t="n">
-        <v>6973939</v>
+        <v>6974089</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2020,11 +2025,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 26084-2025 artfynd.xlsx
+++ b/artfynd/A 26084-2025 artfynd.xlsx
@@ -1658,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128790237</v>
+        <v>128790218</v>
       </c>
       <c r="B11" t="n">
-        <v>91811</v>
+        <v>91526</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,21 +1669,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>622211</v>
+        <v>622266</v>
       </c>
       <c r="R11" t="n">
-        <v>6974148</v>
+        <v>6974203</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1755,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128790218</v>
+        <v>128790237</v>
       </c>
       <c r="B12" t="n">
-        <v>91526</v>
+        <v>91811</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,21 +1766,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>622266</v>
+        <v>622211</v>
       </c>
       <c r="R12" t="n">
-        <v>6974203</v>
+        <v>6974148</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128790230</v>
+        <v>128790241</v>
       </c>
       <c r="B13" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>622493</v>
+        <v>622266</v>
       </c>
       <c r="R13" t="n">
-        <v>6973939</v>
+        <v>6974089</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1923,11 +1923,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1954,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128790241</v>
+        <v>128790230</v>
       </c>
       <c r="B14" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1965,21 +1960,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1989,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>622266</v>
+        <v>622493</v>
       </c>
       <c r="R14" t="n">
-        <v>6974089</v>
+        <v>6973939</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2025,6 +2020,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2051,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128790244</v>
+        <v>128790232</v>
       </c>
       <c r="B15" t="n">
-        <v>91544</v>
+        <v>57883</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2062,21 +2062,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>622463</v>
+        <v>622266</v>
       </c>
       <c r="R15" t="n">
-        <v>6973956</v>
+        <v>6974205</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,10 +2148,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128790232</v>
+        <v>128790244</v>
       </c>
       <c r="B16" t="n">
-        <v>57883</v>
+        <v>91544</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2159,21 +2159,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>622266</v>
+        <v>622463</v>
       </c>
       <c r="R16" t="n">
-        <v>6974205</v>
+        <v>6973956</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2245,32 +2245,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128790238</v>
+        <v>128790234</v>
       </c>
       <c r="B17" t="n">
-        <v>91811</v>
+        <v>80169</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>622403</v>
+        <v>622437</v>
       </c>
       <c r="R17" t="n">
-        <v>6974067</v>
+        <v>6973961</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2342,10 +2342,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128790217</v>
+        <v>128790238</v>
       </c>
       <c r="B18" t="n">
-        <v>91526</v>
+        <v>91811</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2353,21 +2353,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>622309</v>
+        <v>622403</v>
       </c>
       <c r="R18" t="n">
-        <v>6974038</v>
+        <v>6974067</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2439,32 +2439,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128790234</v>
+        <v>128790217</v>
       </c>
       <c r="B19" t="n">
-        <v>80169</v>
+        <v>91526</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>622437</v>
+        <v>622309</v>
       </c>
       <c r="R19" t="n">
-        <v>6973961</v>
+        <v>6974038</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 26084-2025 artfynd.xlsx
+++ b/artfynd/A 26084-2025 artfynd.xlsx
@@ -1462,7 +1462,7 @@
         <v>128790214</v>
       </c>
       <c r="B9" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128790233</v>
+        <v>128790237</v>
       </c>
       <c r="B10" t="n">
-        <v>57883</v>
+        <v>91818</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1567,21 +1567,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>622221</v>
+        <v>622211</v>
       </c>
       <c r="R10" t="n">
-        <v>6974121</v>
+        <v>6974148</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,11 +1627,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1661,7 +1656,7 @@
         <v>128790218</v>
       </c>
       <c r="B11" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128790237</v>
+        <v>128790233</v>
       </c>
       <c r="B12" t="n">
-        <v>91811</v>
+        <v>57885</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,21 +1761,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>622211</v>
+        <v>622221</v>
       </c>
       <c r="R12" t="n">
-        <v>6974148</v>
+        <v>6974121</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1826,6 +1821,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1855,7 +1855,7 @@
         <v>128790241</v>
       </c>
       <c r="B13" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>128790230</v>
       </c>
       <c r="B14" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2051,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128790232</v>
+        <v>128790244</v>
       </c>
       <c r="B15" t="n">
-        <v>57883</v>
+        <v>91551</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2062,21 +2062,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>622266</v>
+        <v>622463</v>
       </c>
       <c r="R15" t="n">
-        <v>6974205</v>
+        <v>6973956</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,10 +2148,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128790244</v>
+        <v>128790232</v>
       </c>
       <c r="B16" t="n">
-        <v>91544</v>
+        <v>57885</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2159,21 +2159,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>622463</v>
+        <v>622266</v>
       </c>
       <c r="R16" t="n">
-        <v>6973956</v>
+        <v>6974205</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2245,32 +2245,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128790234</v>
+        <v>128790217</v>
       </c>
       <c r="B17" t="n">
-        <v>80169</v>
+        <v>91533</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>622437</v>
+        <v>622309</v>
       </c>
       <c r="R17" t="n">
-        <v>6973961</v>
+        <v>6974038</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2345,7 +2345,7 @@
         <v>128790238</v>
       </c>
       <c r="B18" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2439,32 +2439,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128790217</v>
+        <v>128790234</v>
       </c>
       <c r="B19" t="n">
-        <v>91526</v>
+        <v>80173</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>622309</v>
+        <v>622437</v>
       </c>
       <c r="R19" t="n">
-        <v>6974038</v>
+        <v>6973961</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2539,7 +2539,7 @@
         <v>128790235</v>
       </c>
       <c r="B20" t="n">
-        <v>80169</v>
+        <v>80173</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>128790220</v>
       </c>
       <c r="B21" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>128790224</v>
       </c>
       <c r="B22" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2832,10 +2832,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128790245</v>
+        <v>128790228</v>
       </c>
       <c r="B23" t="n">
-        <v>79035</v>
+        <v>57725</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2843,21 +2843,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2867,10 +2867,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>622540</v>
+        <v>622637</v>
       </c>
       <c r="R23" t="n">
-        <v>6973635</v>
+        <v>6973628</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2903,6 +2903,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2929,10 +2934,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128790228</v>
+        <v>128790245</v>
       </c>
       <c r="B24" t="n">
-        <v>57723</v>
+        <v>79039</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2940,21 +2945,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2964,10 +2969,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>622637</v>
+        <v>622540</v>
       </c>
       <c r="R24" t="n">
-        <v>6973628</v>
+        <v>6973635</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3000,11 +3005,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3034,7 +3034,7 @@
         <v>128790225</v>
       </c>
       <c r="B25" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>128790246</v>
       </c>
       <c r="B26" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>128790239</v>
       </c>
       <c r="B27" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>128790216</v>
       </c>
       <c r="B28" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>128790240</v>
       </c>
       <c r="B29" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>128790226</v>
       </c>
       <c r="B30" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>128790222</v>
       </c>
       <c r="B31" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3720,32 +3720,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128790248</v>
+        <v>128790223</v>
       </c>
       <c r="B32" t="n">
-        <v>80175</v>
+        <v>57725</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3755,10 +3755,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>622568</v>
+        <v>622582</v>
       </c>
       <c r="R32" t="n">
-        <v>6973700</v>
+        <v>6973719</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3791,6 +3791,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3817,10 +3822,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128790223</v>
+        <v>128790229</v>
       </c>
       <c r="B33" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3852,10 +3857,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>622582</v>
+        <v>622639</v>
       </c>
       <c r="R33" t="n">
-        <v>6973719</v>
+        <v>6973634</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3919,32 +3924,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128790229</v>
+        <v>128790248</v>
       </c>
       <c r="B34" t="n">
-        <v>57723</v>
+        <v>80179</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3954,10 +3959,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>622639</v>
+        <v>622568</v>
       </c>
       <c r="R34" t="n">
-        <v>6973634</v>
+        <v>6973700</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3990,11 +3995,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4024,7 +4024,7 @@
         <v>128790219</v>
       </c>
       <c r="B35" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         <v>128790231</v>
       </c>
       <c r="B36" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>128790213</v>
       </c>
       <c r="B37" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>128790236</v>
       </c>
       <c r="B38" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4419,10 +4419,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128790221</v>
+        <v>128790247</v>
       </c>
       <c r="B39" t="n">
-        <v>91526</v>
+        <v>79039</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4430,21 +4430,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>622221</v>
+        <v>622267</v>
       </c>
       <c r="R39" t="n">
-        <v>6974149</v>
+        <v>6974268</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4516,10 +4516,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128790247</v>
+        <v>128790227</v>
       </c>
       <c r="B40" t="n">
-        <v>79035</v>
+        <v>57725</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4527,21 +4527,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4551,10 +4551,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>622267</v>
+        <v>622646</v>
       </c>
       <c r="R40" t="n">
-        <v>6974268</v>
+        <v>6973525</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4587,6 +4587,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4613,10 +4618,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128790227</v>
+        <v>128790221</v>
       </c>
       <c r="B41" t="n">
-        <v>57723</v>
+        <v>91533</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4624,21 +4629,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4648,10 +4653,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>622646</v>
+        <v>622221</v>
       </c>
       <c r="R41" t="n">
-        <v>6973525</v>
+        <v>6974149</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4684,11 +4689,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 26084-2025 artfynd.xlsx
+++ b/artfynd/A 26084-2025 artfynd.xlsx
@@ -2832,10 +2832,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128790228</v>
+        <v>128790245</v>
       </c>
       <c r="B23" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2843,21 +2843,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2867,10 +2867,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>622637</v>
+        <v>622540</v>
       </c>
       <c r="R23" t="n">
-        <v>6973628</v>
+        <v>6973635</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2903,11 +2903,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2934,10 +2929,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128790245</v>
+        <v>128790228</v>
       </c>
       <c r="B24" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2945,21 +2940,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2969,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>622540</v>
+        <v>622637</v>
       </c>
       <c r="R24" t="n">
-        <v>6973635</v>
+        <v>6973628</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3005,6 +3000,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3327,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128790216</v>
+        <v>128790240</v>
       </c>
       <c r="B28" t="n">
-        <v>91533</v>
+        <v>80144</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3338,21 +3338,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>622450</v>
+        <v>622574</v>
       </c>
       <c r="R28" t="n">
-        <v>6974017</v>
+        <v>6973694</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3424,10 +3424,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128790240</v>
+        <v>128790216</v>
       </c>
       <c r="B29" t="n">
-        <v>80144</v>
+        <v>91533</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3435,21 +3435,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3459,10 +3459,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>622574</v>
+        <v>622450</v>
       </c>
       <c r="R29" t="n">
-        <v>6973694</v>
+        <v>6974017</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 26084-2025 artfynd.xlsx
+++ b/artfynd/A 26084-2025 artfynd.xlsx
@@ -1462,7 +1462,7 @@
         <v>128790214</v>
       </c>
       <c r="B9" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128790237</v>
+        <v>128790233</v>
       </c>
       <c r="B10" t="n">
-        <v>91818</v>
+        <v>57885</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1567,21 +1567,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>622211</v>
+        <v>622221</v>
       </c>
       <c r="R10" t="n">
-        <v>6974148</v>
+        <v>6974121</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,6 +1627,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,7 +1661,7 @@
         <v>128790218</v>
       </c>
       <c r="B11" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1750,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128790233</v>
+        <v>128790237</v>
       </c>
       <c r="B12" t="n">
-        <v>57885</v>
+        <v>91825</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1761,21 +1766,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>622221</v>
+        <v>622211</v>
       </c>
       <c r="R12" t="n">
-        <v>6974121</v>
+        <v>6974148</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1821,11 +1826,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2054,7 +2054,7 @@
         <v>128790244</v>
       </c>
       <c r="B15" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2245,10 +2245,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128790217</v>
+        <v>128790238</v>
       </c>
       <c r="B17" t="n">
-        <v>91533</v>
+        <v>91825</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2256,21 +2256,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>622309</v>
+        <v>622403</v>
       </c>
       <c r="R17" t="n">
-        <v>6974038</v>
+        <v>6974067</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2342,10 +2342,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128790238</v>
+        <v>128790217</v>
       </c>
       <c r="B18" t="n">
-        <v>91818</v>
+        <v>91540</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2353,21 +2353,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>622403</v>
+        <v>622309</v>
       </c>
       <c r="R18" t="n">
-        <v>6974067</v>
+        <v>6974038</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2636,7 +2636,7 @@
         <v>128790220</v>
       </c>
       <c r="B21" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128790240</v>
+        <v>128790216</v>
       </c>
       <c r="B28" t="n">
-        <v>80144</v>
+        <v>91540</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3338,21 +3338,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>622574</v>
+        <v>622450</v>
       </c>
       <c r="R28" t="n">
-        <v>6973694</v>
+        <v>6974017</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3424,10 +3424,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128790216</v>
+        <v>128790240</v>
       </c>
       <c r="B29" t="n">
-        <v>91533</v>
+        <v>80144</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3435,21 +3435,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3459,10 +3459,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>622450</v>
+        <v>622574</v>
       </c>
       <c r="R29" t="n">
-        <v>6974017</v>
+        <v>6973694</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3626,7 +3626,7 @@
         <v>128790222</v>
       </c>
       <c r="B31" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3720,32 +3720,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128790223</v>
+        <v>128790248</v>
       </c>
       <c r="B32" t="n">
-        <v>57725</v>
+        <v>80179</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3755,10 +3755,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>622582</v>
+        <v>622568</v>
       </c>
       <c r="R32" t="n">
-        <v>6973719</v>
+        <v>6973700</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3791,11 +3791,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3822,7 +3817,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128790229</v>
+        <v>128790223</v>
       </c>
       <c r="B33" t="n">
         <v>57725</v>
@@ -3857,10 +3852,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>622639</v>
+        <v>622582</v>
       </c>
       <c r="R33" t="n">
-        <v>6973634</v>
+        <v>6973719</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3924,32 +3919,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128790248</v>
+        <v>128790229</v>
       </c>
       <c r="B34" t="n">
-        <v>80179</v>
+        <v>57725</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3959,10 +3954,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>622568</v>
+        <v>622639</v>
       </c>
       <c r="R34" t="n">
-        <v>6973700</v>
+        <v>6973634</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3995,6 +3990,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4024,7 +4024,7 @@
         <v>128790219</v>
       </c>
       <c r="B35" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>128790213</v>
       </c>
       <c r="B37" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4419,10 +4419,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128790247</v>
+        <v>128790221</v>
       </c>
       <c r="B39" t="n">
-        <v>79039</v>
+        <v>91540</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4430,21 +4430,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>622267</v>
+        <v>622221</v>
       </c>
       <c r="R39" t="n">
-        <v>6974268</v>
+        <v>6974149</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4516,10 +4516,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128790227</v>
+        <v>128790247</v>
       </c>
       <c r="B40" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4527,21 +4527,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4551,10 +4551,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>622646</v>
+        <v>622267</v>
       </c>
       <c r="R40" t="n">
-        <v>6973525</v>
+        <v>6974268</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4587,11 +4587,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4618,10 +4613,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128790221</v>
+        <v>128790227</v>
       </c>
       <c r="B41" t="n">
-        <v>91533</v>
+        <v>57725</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4629,21 +4624,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4653,10 +4648,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>622221</v>
+        <v>622646</v>
       </c>
       <c r="R41" t="n">
-        <v>6974149</v>
+        <v>6973525</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4689,6 +4684,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 26084-2025 artfynd.xlsx
+++ b/artfynd/A 26084-2025 artfynd.xlsx
@@ -1462,7 +1462,7 @@
         <v>128790214</v>
       </c>
       <c r="B9" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128790233</v>
+        <v>128790218</v>
       </c>
       <c r="B10" t="n">
-        <v>57885</v>
+        <v>91542</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1567,21 +1567,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>622221</v>
+        <v>622266</v>
       </c>
       <c r="R10" t="n">
-        <v>6974121</v>
+        <v>6974203</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,11 +1627,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1658,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128790218</v>
+        <v>128790233</v>
       </c>
       <c r="B11" t="n">
-        <v>91540</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,21 +1664,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1693,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>622266</v>
+        <v>622221</v>
       </c>
       <c r="R11" t="n">
-        <v>6974203</v>
+        <v>6974121</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,6 +1724,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1758,7 +1758,7 @@
         <v>128790237</v>
       </c>
       <c r="B12" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128790241</v>
+        <v>128790230</v>
       </c>
       <c r="B13" t="n">
-        <v>80144</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>622266</v>
+        <v>622493</v>
       </c>
       <c r="R13" t="n">
-        <v>6974089</v>
+        <v>6973939</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1923,6 +1923,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128790230</v>
+        <v>128790241</v>
       </c>
       <c r="B14" t="n">
-        <v>57725</v>
+        <v>80146</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1960,21 +1965,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>622493</v>
+        <v>622266</v>
       </c>
       <c r="R14" t="n">
-        <v>6973939</v>
+        <v>6974089</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2020,11 +2025,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2054,7 +2054,7 @@
         <v>128790244</v>
       </c>
       <c r="B15" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>128790232</v>
       </c>
       <c r="B16" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>128790238</v>
       </c>
       <c r="B17" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>128790217</v>
       </c>
       <c r="B18" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>128790234</v>
       </c>
       <c r="B19" t="n">
-        <v>80173</v>
+        <v>80175</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>128790235</v>
       </c>
       <c r="B20" t="n">
-        <v>80173</v>
+        <v>80175</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>128790220</v>
       </c>
       <c r="B21" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>128790224</v>
       </c>
       <c r="B22" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>128790245</v>
       </c>
       <c r="B23" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>128790228</v>
       </c>
       <c r="B24" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         <v>128790225</v>
       </c>
       <c r="B25" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>128790246</v>
       </c>
       <c r="B26" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>128790239</v>
       </c>
       <c r="B27" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>128790216</v>
       </c>
       <c r="B28" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>128790240</v>
       </c>
       <c r="B29" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>128790226</v>
       </c>
       <c r="B30" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>128790222</v>
       </c>
       <c r="B31" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3720,32 +3720,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128790248</v>
+        <v>128790223</v>
       </c>
       <c r="B32" t="n">
-        <v>80179</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3755,10 +3755,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>622568</v>
+        <v>622582</v>
       </c>
       <c r="R32" t="n">
-        <v>6973700</v>
+        <v>6973719</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3791,6 +3791,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3817,10 +3822,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128790223</v>
+        <v>128790229</v>
       </c>
       <c r="B33" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3852,10 +3857,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>622582</v>
+        <v>622639</v>
       </c>
       <c r="R33" t="n">
-        <v>6973719</v>
+        <v>6973634</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3919,32 +3924,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128790229</v>
+        <v>128790248</v>
       </c>
       <c r="B34" t="n">
-        <v>57725</v>
+        <v>80181</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3954,10 +3959,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>622639</v>
+        <v>622568</v>
       </c>
       <c r="R34" t="n">
-        <v>6973634</v>
+        <v>6973700</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3990,11 +3995,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4021,10 +4021,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128790219</v>
+        <v>128790231</v>
       </c>
       <c r="B35" t="n">
-        <v>91540</v>
+        <v>57887</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4032,21 +4032,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4056,10 +4056,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>622240</v>
+        <v>622564</v>
       </c>
       <c r="R35" t="n">
-        <v>6974241</v>
+        <v>6973544</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4092,6 +4092,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4118,10 +4123,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128790231</v>
+        <v>128790219</v>
       </c>
       <c r="B36" t="n">
-        <v>57885</v>
+        <v>91542</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4129,21 +4134,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4153,10 +4158,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>622564</v>
+        <v>622240</v>
       </c>
       <c r="R36" t="n">
-        <v>6973544</v>
+        <v>6974241</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4189,11 +4194,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4223,7 +4223,7 @@
         <v>128790213</v>
       </c>
       <c r="B37" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>128790236</v>
       </c>
       <c r="B38" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>128790221</v>
       </c>
       <c r="B39" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>128790247</v>
       </c>
       <c r="B40" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4616,7 +4616,7 @@
         <v>128790227</v>
       </c>
       <c r="B41" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 26084-2025 artfynd.xlsx
+++ b/artfynd/A 26084-2025 artfynd.xlsx
@@ -1556,10 +1556,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128790218</v>
+        <v>128790237</v>
       </c>
       <c r="B10" t="n">
-        <v>91542</v>
+        <v>91827</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1567,21 +1567,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>622266</v>
+        <v>622211</v>
       </c>
       <c r="R10" t="n">
-        <v>6974203</v>
+        <v>6974148</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128790233</v>
+        <v>128790218</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>91542</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,21 +1664,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>622221</v>
+        <v>622266</v>
       </c>
       <c r="R11" t="n">
-        <v>6974121</v>
+        <v>6974203</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,11 +1724,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128790237</v>
+        <v>128790233</v>
       </c>
       <c r="B12" t="n">
-        <v>91827</v>
+        <v>57887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,21 +1761,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>622211</v>
+        <v>622221</v>
       </c>
       <c r="R12" t="n">
-        <v>6974148</v>
+        <v>6974121</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1826,6 +1821,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128790230</v>
+        <v>128790241</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>622493</v>
+        <v>622266</v>
       </c>
       <c r="R13" t="n">
-        <v>6973939</v>
+        <v>6974089</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1923,11 +1923,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1954,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128790241</v>
+        <v>128790230</v>
       </c>
       <c r="B14" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1965,21 +1960,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1989,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>622266</v>
+        <v>622493</v>
       </c>
       <c r="R14" t="n">
-        <v>6974089</v>
+        <v>6973939</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2025,6 +2020,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2342,32 +2342,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128790217</v>
+        <v>128790234</v>
       </c>
       <c r="B18" t="n">
-        <v>91542</v>
+        <v>80175</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>622309</v>
+        <v>622437</v>
       </c>
       <c r="R18" t="n">
-        <v>6974038</v>
+        <v>6973961</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2439,32 +2439,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128790234</v>
+        <v>128790217</v>
       </c>
       <c r="B19" t="n">
-        <v>80175</v>
+        <v>91542</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>622437</v>
+        <v>622309</v>
       </c>
       <c r="R19" t="n">
-        <v>6973961</v>
+        <v>6974038</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -4021,10 +4021,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128790231</v>
+        <v>128790219</v>
       </c>
       <c r="B35" t="n">
-        <v>57887</v>
+        <v>91542</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4032,21 +4032,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4056,10 +4056,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>622564</v>
+        <v>622240</v>
       </c>
       <c r="R35" t="n">
-        <v>6973544</v>
+        <v>6974241</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4092,11 +4092,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4123,10 +4118,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128790219</v>
+        <v>128790231</v>
       </c>
       <c r="B36" t="n">
-        <v>91542</v>
+        <v>57887</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4134,21 +4129,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4158,10 +4153,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>622240</v>
+        <v>622564</v>
       </c>
       <c r="R36" t="n">
-        <v>6974241</v>
+        <v>6973544</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4194,6 +4189,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4516,10 +4516,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128790247</v>
+        <v>128790227</v>
       </c>
       <c r="B40" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4527,21 +4527,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4551,10 +4551,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>622267</v>
+        <v>622646</v>
       </c>
       <c r="R40" t="n">
-        <v>6974268</v>
+        <v>6973525</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4587,6 +4587,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4613,10 +4618,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128790227</v>
+        <v>128790247</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4624,21 +4629,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4648,10 +4653,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>622646</v>
+        <v>622267</v>
       </c>
       <c r="R41" t="n">
-        <v>6973525</v>
+        <v>6974268</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4684,11 +4689,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 26084-2025 artfynd.xlsx
+++ b/artfynd/A 26084-2025 artfynd.xlsx
@@ -2832,10 +2832,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128790245</v>
+        <v>128790228</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2843,21 +2843,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2867,10 +2867,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>622540</v>
+        <v>622637</v>
       </c>
       <c r="R23" t="n">
-        <v>6973635</v>
+        <v>6973628</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2903,6 +2903,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2929,10 +2934,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128790228</v>
+        <v>128790245</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2940,21 +2945,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2964,10 +2969,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>622637</v>
+        <v>622540</v>
       </c>
       <c r="R24" t="n">
-        <v>6973628</v>
+        <v>6973635</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3000,11 +3005,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3720,32 +3720,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128790223</v>
+        <v>128790248</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>80181</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3755,10 +3755,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>622582</v>
+        <v>622568</v>
       </c>
       <c r="R32" t="n">
-        <v>6973719</v>
+        <v>6973700</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3791,11 +3791,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3822,7 +3817,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128790229</v>
+        <v>128790223</v>
       </c>
       <c r="B33" t="n">
         <v>57727</v>
@@ -3857,10 +3852,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>622639</v>
+        <v>622582</v>
       </c>
       <c r="R33" t="n">
-        <v>6973634</v>
+        <v>6973719</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3924,32 +3919,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128790248</v>
+        <v>128790229</v>
       </c>
       <c r="B34" t="n">
-        <v>80181</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3959,10 +3954,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>622568</v>
+        <v>622639</v>
       </c>
       <c r="R34" t="n">
-        <v>6973700</v>
+        <v>6973634</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3995,6 +3990,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 26084-2025 artfynd.xlsx
+++ b/artfynd/A 26084-2025 artfynd.xlsx
@@ -1462,7 +1462,7 @@
         <v>128790214</v>
       </c>
       <c r="B9" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>128790237</v>
       </c>
       <c r="B10" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>128790218</v>
       </c>
       <c r="B11" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>128790244</v>
       </c>
       <c r="B15" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2245,10 +2245,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128790238</v>
+        <v>128790217</v>
       </c>
       <c r="B17" t="n">
-        <v>91827</v>
+        <v>91540</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2256,21 +2256,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>622403</v>
+        <v>622309</v>
       </c>
       <c r="R17" t="n">
-        <v>6974067</v>
+        <v>6974038</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2342,32 +2342,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128790234</v>
+        <v>128790238</v>
       </c>
       <c r="B18" t="n">
-        <v>80175</v>
+        <v>91837</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>622437</v>
+        <v>622403</v>
       </c>
       <c r="R18" t="n">
-        <v>6973961</v>
+        <v>6974067</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2439,32 +2439,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128790217</v>
+        <v>128790234</v>
       </c>
       <c r="B19" t="n">
-        <v>91542</v>
+        <v>80175</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>622309</v>
+        <v>622437</v>
       </c>
       <c r="R19" t="n">
-        <v>6974038</v>
+        <v>6973961</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2636,7 +2636,7 @@
         <v>128790220</v>
       </c>
       <c r="B21" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2832,10 +2832,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128790228</v>
+        <v>128790245</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2843,21 +2843,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2867,10 +2867,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>622637</v>
+        <v>622540</v>
       </c>
       <c r="R23" t="n">
-        <v>6973628</v>
+        <v>6973635</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2903,11 +2903,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2934,10 +2929,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128790245</v>
+        <v>128790228</v>
       </c>
       <c r="B24" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2945,21 +2940,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2969,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>622540</v>
+        <v>622637</v>
       </c>
       <c r="R24" t="n">
-        <v>6973635</v>
+        <v>6973628</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3005,6 +3000,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3133,10 +3133,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128790246</v>
+        <v>128790239</v>
       </c>
       <c r="B26" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3144,21 +3144,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>622548</v>
+        <v>622436</v>
       </c>
       <c r="R26" t="n">
-        <v>6973896</v>
+        <v>6973957</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3230,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128790239</v>
+        <v>128790246</v>
       </c>
       <c r="B27" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3241,21 +3241,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>622436</v>
+        <v>622548</v>
       </c>
       <c r="R27" t="n">
-        <v>6973957</v>
+        <v>6973896</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128790216</v>
+        <v>128790240</v>
       </c>
       <c r="B28" t="n">
-        <v>91542</v>
+        <v>80146</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3338,21 +3338,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>622450</v>
+        <v>622574</v>
       </c>
       <c r="R28" t="n">
-        <v>6974017</v>
+        <v>6973694</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3424,10 +3424,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128790240</v>
+        <v>128790216</v>
       </c>
       <c r="B29" t="n">
-        <v>80146</v>
+        <v>91540</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3435,21 +3435,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3459,10 +3459,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>622574</v>
+        <v>622450</v>
       </c>
       <c r="R29" t="n">
-        <v>6973694</v>
+        <v>6974017</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3626,7 +3626,7 @@
         <v>128790222</v>
       </c>
       <c r="B31" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4021,10 +4021,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128790219</v>
+        <v>128790231</v>
       </c>
       <c r="B35" t="n">
-        <v>91542</v>
+        <v>57887</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4032,21 +4032,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4056,10 +4056,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>622240</v>
+        <v>622564</v>
       </c>
       <c r="R35" t="n">
-        <v>6974241</v>
+        <v>6973544</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4092,6 +4092,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4118,10 +4123,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128790231</v>
+        <v>128790219</v>
       </c>
       <c r="B36" t="n">
-        <v>57887</v>
+        <v>91540</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4129,21 +4134,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4153,10 +4158,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>622564</v>
+        <v>622240</v>
       </c>
       <c r="R36" t="n">
-        <v>6973544</v>
+        <v>6974241</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4189,11 +4194,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Lockläte/övriga läten</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4223,7 +4223,7 @@
         <v>128790213</v>
       </c>
       <c r="B37" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4419,10 +4419,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128790221</v>
+        <v>128790227</v>
       </c>
       <c r="B39" t="n">
-        <v>91542</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4430,21 +4430,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>622221</v>
+        <v>622646</v>
       </c>
       <c r="R39" t="n">
-        <v>6974149</v>
+        <v>6973525</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4490,6 +4490,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4516,10 +4521,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128790227</v>
+        <v>128790221</v>
       </c>
       <c r="B40" t="n">
-        <v>57727</v>
+        <v>91540</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4527,21 +4532,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4551,10 +4556,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>622646</v>
+        <v>622221</v>
       </c>
       <c r="R40" t="n">
-        <v>6973525</v>
+        <v>6974149</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4587,11 +4592,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 26084-2025 artfynd.xlsx
+++ b/artfynd/A 26084-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128790237</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101505316</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128790217</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128790218</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128790219</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128790220</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128790221</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128790222</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101505315</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128790213</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128790247</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128790241</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128790235</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2035,6 +2105,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128790236</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2132,6 +2207,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128790232</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2234,8 +2314,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128790233</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>